--- a/reports/Debug-purgatory-20260105/For The Week Ending (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260105/For The Week Ending (Prior Year)_Visits.xlsx
@@ -34,10 +34,10 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
+    <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Comp Tickets</t>
   </si>
 </sst>
 </file>
@@ -431,7 +431,7 @@
         <v>45663</v>
       </c>
       <c r="C2" s="2">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,7 +445,7 @@
         <v>45663</v>
       </c>
       <c r="C3" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -459,7 +459,7 @@
         <v>45663</v>
       </c>
       <c r="C4" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -473,7 +473,7 @@
         <v>45663</v>
       </c>
       <c r="C5" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -487,10 +487,10 @@
         <v>45663</v>
       </c>
       <c r="C6" s="2">
-        <v>1071</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,10 +501,10 @@
         <v>45663</v>
       </c>
       <c r="C7" s="2">
-        <v>3</v>
+        <v>238</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,7 +515,7 @@
         <v>45663</v>
       </c>
       <c r="C8" s="2">
-        <v>69</v>
+        <v>899</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -529,7 +529,7 @@
         <v>45663</v>
       </c>
       <c r="C9" s="2">
-        <v>238</v>
+        <v>1071</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>7</v>
@@ -543,7 +543,7 @@
         <v>45663</v>
       </c>
       <c r="C10" s="2">
-        <v>899</v>
+        <v>3</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -557,7 +557,7 @@
         <v>45663</v>
       </c>
       <c r="C11" s="2">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
